--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14049,14 +14049,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUG · Top 100 corp · ordenado por CR únicos ↓</t>
+          <t>CUG · Top 100 corp · ordenado por Eficacia ↑ (menor a mayor)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14118,37 +14118,37 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Station Casinos</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>190498</v>
+        <v>162</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>173894</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>4173</v>
+        <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.9128389799367972</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.02190574179256475</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -14158,37 +14158,37 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, HBSI, Internal</t>
+          <t>HotelBeds Apitude</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>109482</v>
+        <v>48</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>106415</v>
+        <v>20</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1382</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.971986262581977</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.01262307959299246</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -14198,37 +14198,37 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Oyo Rooms</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>HotelBeds Apitude</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>70556</v>
+        <v>27</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>67113</v>
+        <v>15</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.9512018821928681</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.01527864391405408</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -14238,28 +14238,28 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Iberostar</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HBSI, HotelBeds Apitude, Internal, Siteminder, SynXis, Travelclick</t>
+          <t>HBSI, Internal</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>36276</v>
+        <v>666</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>29671</v>
+        <v>433</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1303</v>
+        <v>6</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.8179236961076194</v>
+        <v>0.6501501501501501</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0.03591906494652112</v>
+        <v>0.009009009009009009</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14278,37 +14278,37 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal, SynXis</t>
+          <t>HBSI, Internal</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>23986</v>
+        <v>2310</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>22617</v>
+        <v>1639</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.9429250396064371</v>
+        <v>0.7095238095238096</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.003960643708830151</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14358,37 +14358,37 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>DerbySoft, Expedia, HBSI, HotelBeds Apitude, Internal, Siteminder, SynXis, Travelclick</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>9756</v>
+        <v>36276</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>9072</v>
+        <v>29671</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>184</v>
+        <v>1303</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.9298892988929889</v>
+        <v>0.8179236961076194</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.01886018860188602</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.03591906494652112</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14398,37 +14398,37 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>Presidente Intercontinental</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Expedia, Internal</t>
+          <t>DerbySoft, Internal</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>8454</v>
+        <v>910</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>7956</v>
+        <v>797</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.9410929737402413</v>
+        <v>0.8758241758241758</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.00532292405961675</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.06263736263736264</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14438,37 +14438,37 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Best Western</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft, Expedia</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>8138</v>
+        <v>5357</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>7946</v>
+        <v>4728</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.9764069796018677</v>
+        <v>0.8825835355609483</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.02162693536495454</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.005600149337315662</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -14487,19 +14487,19 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>5973</v>
+        <v>1796</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>5503</v>
+        <v>1610</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.9213125732462749</v>
+        <v>0.8964365256124721</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.05993638037836933</v>
+        <v>0.04342984409799554</v>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Dann</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -14527,28 +14527,28 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>5533</v>
+        <v>324</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>5508</v>
+        <v>292</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.995481655521417</v>
+        <v>0.9012345679012346</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.02801373576721489</v>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14558,28 +14558,28 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Best Western</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>5357</v>
+        <v>3523</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>4728</v>
+        <v>3193</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.8825835355609483</v>
+        <v>0.9063298325290945</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.005600149337315662</v>
+        <v>0.009934714731762702</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14598,37 +14598,37 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Palladium Hotel Group</t>
+          <t>Grupo Welcome</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>5140</v>
+        <v>89</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>5140</v>
+        <v>81</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1</v>
+        <v>0.9101123595505618</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.1208171206225681</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14638,37 +14638,37 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>DerbySoft, Expedia, Internal</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>4610</v>
+        <v>190498</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>4594</v>
+        <v>173894</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>19</v>
+        <v>4173</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.996529284164859</v>
+        <v>0.9128389799367972</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.004121475054229935</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.02190574179256475</v>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14678,32 +14678,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>4113</v>
+        <v>5973</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>4106</v>
+        <v>5503</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>113</v>
+        <v>358</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.9982980792608801</v>
+        <v>0.9213125732462749</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.0274738633600778</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.05993638037836933</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -14718,28 +14718,28 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>DerbySoft, Internal</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>3523</v>
+        <v>9756</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>3193</v>
+        <v>9072</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.9063298325290945</v>
+        <v>0.9298892988929889</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.009934714731762702</v>
+        <v>0.01886018860188602</v>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14758,37 +14758,37 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Expedia, Internal</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>3499</v>
+        <v>8454</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>3459</v>
+        <v>7956</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>395</v>
+        <v>45</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.9885681623320949</v>
+        <v>0.9410929737402413</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.112889396970563</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.00532292405961675</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14798,32 +14798,32 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal, SynXis</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>3339</v>
+        <v>23986</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3273</v>
+        <v>22617</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.9802336028751123</v>
+        <v>0.9429250396064371</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.007487271638215035</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.003960643708830151</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -14847,28 +14847,28 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>3296</v>
+        <v>1736</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3295</v>
+        <v>1644</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.9996966019417476</v>
+        <v>0.9470046082949308</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.00424757281553398</v>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
+        <v>0.08525345622119816</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14878,28 +14878,28 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>3107</v>
+        <v>70556</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>2998</v>
+        <v>67113</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>155</v>
+        <v>1078</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.9649179272610235</v>
+        <v>0.9512018821928681</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0.04988735114258127</v>
+        <v>0.01527864391405408</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14918,37 +14918,37 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Internal, SynXis</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>2311</v>
+        <v>977</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>2265</v>
+        <v>937</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.9800951968844656</v>
+        <v>0.9590583418628454</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.03807875378623973</v>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01740020470829069</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14958,37 +14958,37 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>Las Brisas</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>HBSI, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>2310</v>
+        <v>2201</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1639</v>
+        <v>2111</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.7095238095238096</v>
+        <v>0.9591094956837801</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>0.01818181818181818</v>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0.04497955474784189</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Park Royal</t>
+          <t>Americas Hotels Group</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -15007,23 +15007,23 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2256</v>
+        <v>292</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2214</v>
+        <v>281</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.9813829787234043</v>
+        <v>0.9623287671232876</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.02526595744680851</v>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.05136986301369863</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>Hoteles Geh Suites</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -15047,28 +15047,28 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2236</v>
+        <v>644</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>2209</v>
+        <v>621</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.9879248658318426</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>0.02415026833631485</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01397515527950311</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15078,28 +15078,28 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>2201</v>
+        <v>3107</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>2111</v>
+        <v>2998</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.9591094956837801</v>
+        <v>0.9649179272610235</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.04497955474784189</v>
+        <v>0.04988735114258127</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -15118,28 +15118,28 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Palace</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft, HBSI, Internal</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>1979</v>
+        <v>109482</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>1974</v>
+        <v>106415</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>148</v>
+        <v>1382</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.9974734714502274</v>
+        <v>0.971986262581977</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>0.07478524507326932</v>
+        <v>0.01262307959299246</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15158,32 +15158,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Royalton Hotels &amp; Resorts</t>
+          <t>Hoteles Movich</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>1796</v>
+        <v>113</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1610</v>
+        <v>110</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.8964365256124721</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.04342984409799554</v>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.06194690265486726</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -15198,37 +15198,37 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1736</v>
+        <v>8138</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>1644</v>
+        <v>7946</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.9470046082949308</v>
+        <v>0.9764069796018677</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>0.08525345622119816</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
+        <v>0.02162693536495454</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15238,28 +15238,28 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Oasis</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal, SynXis</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1704</v>
+        <v>2311</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1692</v>
+        <v>2265</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.9929577464788732</v>
+        <v>0.9800951968844656</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.007042253521126761</v>
+        <v>0.03807875378623973</v>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15278,28 +15278,28 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Internal, Siteminder</t>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>1444</v>
+        <v>3339</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1429</v>
+        <v>3273</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.989612188365651</v>
+        <v>0.9802336028751123</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0.01246537396121884</v>
+        <v>0.007487271638215035</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Decameron</t>
+          <t>Park Royal</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -15327,19 +15327,19 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>1237</v>
+        <v>2256</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>1232</v>
+        <v>2214</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.9959579628132579</v>
+        <v>0.9813829787234043</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.04122877930476961</v>
+        <v>0.02526595744680851</v>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
@@ -15358,32 +15358,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>977</v>
+        <v>186</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>937</v>
+        <v>183</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.9590583418628454</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>0.01740020470829069</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -15398,37 +15398,37 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Presidente Intercontinental</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>910</v>
+        <v>2236</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>797</v>
+        <v>2209</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.8758241758241758</v>
+        <v>0.9879248658318426</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.06263736263736264</v>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.02415026833631485</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15438,28 +15438,28 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>890</v>
+        <v>3499</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>885</v>
+        <v>3459</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>44</v>
+        <v>395</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.9943820224719101</v>
+        <v>0.9885681623320949</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>0.04943820224719101</v>
+        <v>0.112889396970563</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -15478,28 +15478,28 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Sandos</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal, Siteminder</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>869</v>
+        <v>1444</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>864</v>
+        <v>1429</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.9942462600690449</v>
+        <v>0.989612188365651</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.04027617951668585</v>
+        <v>0.01246537396121884</v>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15518,37 +15518,37 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Iberostar</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>HBSI, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>666</v>
+        <v>108</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.6501501501501501</v>
+        <v>0.9907407407407407</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>0.009009009009009009</v>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15558,37 +15558,37 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Geh Suites</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal, Travelclick</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9920760697305864</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.01397515527950311</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.07290015847860538</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15598,28 +15598,28 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>Oasis</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Internal, Travelclick</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>631</v>
+        <v>1704</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>626</v>
+        <v>1692</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.9920760697305864</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0.07290015847860538</v>
+        <v>0.007042253521126761</v>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -15647,19 +15647,19 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>474</v>
+        <v>869</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>474</v>
+        <v>864</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>1</v>
+        <v>0.9942462600690449</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.08227848101265822</v>
+        <v>0.04027617951668585</v>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
@@ -15678,28 +15678,28 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>El Dorado San Andrés</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>411</v>
+        <v>890</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>411</v>
+        <v>885</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>1</v>
+        <v>0.9943820224719101</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>0.0267639902676399</v>
+        <v>0.04943820224719101</v>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Solar</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -15727,19 +15727,19 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>327</v>
+        <v>5533</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>327</v>
+        <v>5508</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1</v>
+        <v>0.995481655521417</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.08868501529051988</v>
+        <v>0.02801373576721489</v>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Dann</t>
+          <t>Decameron</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -15767,28 +15767,28 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>324</v>
+        <v>1237</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>292</v>
+        <v>1232</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.9012345679012346</v>
+        <v>0.9959579628132579</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.01851851851851852</v>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.04122877930476961</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15798,37 +15798,37 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Americas Hotels Group</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>292</v>
+        <v>4610</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>281</v>
+        <v>4594</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.9623287671232876</v>
+        <v>0.996529284164859</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.05136986301369863</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.004121475054229935</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Pueblo Bonito</t>
+          <t>Palace</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -15847,19 +15847,19 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>255</v>
+        <v>1979</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>255</v>
+        <v>1974</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1</v>
+        <v>0.9974734714502274</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>0.02745098039215686</v>
+        <v>0.07478524507326932</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -15878,28 +15878,28 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>186</v>
+        <v>4113</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>183</v>
+        <v>4106</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9982980792608801</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0274738633600778</v>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15918,37 +15918,37 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Station Casinos</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>162</v>
+        <v>3296</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0</v>
+        <v>3295</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0</v>
+        <v>0.9996966019417476</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.00424757281553398</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>EM Hotels</t>
+          <t>Palladium Hotel Group</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -15967,19 +15967,19 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>145</v>
+        <v>5140</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>145</v>
+        <v>5140</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="G52" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0</v>
+        <v>0.1208171206225681</v>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15998,28 +15998,28 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Dorado Plaza</t>
+          <t>El Dorado San Andrés</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>123</v>
+        <v>411</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>123</v>
+        <v>411</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>0</v>
+        <v>0.0267639902676399</v>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16038,12 +16038,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Villa Group</t>
+          <t>Dorado Plaza</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D54" s="12" t="n">
@@ -16053,13 +16053,13 @@
         <v>123</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0.02439024390243903</v>
+        <v>0</v>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16078,28 +16078,28 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Movich</t>
+          <t>EM Hotels</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.9734513274336283</v>
+        <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>0.06194690265486726</v>
+        <v>0</v>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Hoteles Solar</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -16127,19 +16127,19 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>108</v>
+        <v>327</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.9907407407407407</v>
+        <v>1</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0.04629629629629629</v>
+        <v>0.08868501529051988</v>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Oxo Hotel</t>
+          <t>Pueblo Bonito</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -16167,19 +16167,19 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>96</v>
+        <v>255</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>96</v>
+        <v>255</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G57" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.02745098039215686</v>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Grupo Welcome</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -16207,28 +16207,28 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>89</v>
+        <v>474</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="F58" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G58" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="13" t="n">
-        <v>0.9101123595505618</v>
-      </c>
       <c r="H58" s="13" t="n">
-        <v>0.01123595505617977</v>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.08227848101265822</v>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16238,19 +16238,19 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Atlantica</t>
+          <t>Oxo Hotel</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
@@ -16259,7 +16259,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>0.0119047619047619</v>
+        <v>0.01041666666666667</v>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
@@ -16278,28 +16278,28 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Lomas Hospitality</t>
+          <t>Atlantica</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>0.09230769230769231</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16318,37 +16318,37 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>Villa Group</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>HotelBeds Apitude</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>Lomas Hospitality</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -16367,19 +16367,19 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G62" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.09230769230769231</v>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Estelar</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -16413,13 +16413,13 @@
         <v>33</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
@@ -16478,19 +16478,19 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Costa del Sol</t>
+          <t>Estelar</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -16499,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
@@ -16518,37 +16518,37 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Oyo Rooms</t>
+          <t>Costa del Sol</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>HotelBeds Apitude</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20228,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18303,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14709,7 +14709,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18303,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
